--- a/GameConfig/Datas/关卡/地图相关配置表.xlsx
+++ b/GameConfig/Datas/关卡/地图相关配置表.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub_Project\DGame_Fantasy\GameConfig\Datas\关卡\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEDDB00E-21E0-434E-985D-CF78BCC74358}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="地图配置表" sheetId="4" r:id="rId1"/>
@@ -28,7 +34,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -142,9 +148,6 @@
     <t>路径点_4</t>
   </si>
   <si>
-    <t>Battleground/Bkg_1_1_nongchang</t>
-  </si>
-  <si>
     <t>ID</t>
   </si>
   <si>
@@ -260,19 +263,17 @@
   </si>
   <si>
     <t>备注*策划</t>
+  </si>
+  <si>
+    <t>nongchang</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="24">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -284,12 +285,14 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -297,6 +300,7 @@
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -305,154 +309,42 @@
       <sz val="10"/>
       <color theme="0"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -485,13 +377,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799584948271126"/>
+        <fgColor theme="9" tint="0.79955442976165048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -503,174 +395,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799615466780602"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.79958494827112647"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -695,268 +425,32 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="0" tint="-0.149174474318674"/>
+        <color theme="0" tint="-0.14914395580919829"/>
       </left>
       <right style="thin">
-        <color theme="0" tint="-0.149174474318674"/>
+        <color theme="0" tint="-0.14914395580919829"/>
       </right>
       <top style="thin">
-        <color theme="0" tint="-0.149174474318674"/>
+        <color theme="0" tint="-0.14914395580919829"/>
       </top>
       <bottom style="thin">
-        <color theme="0" tint="-0.149174474318674"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+        <color theme="0" tint="-0.14914395580919829"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="51">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -964,28 +458,28 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="22" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="23" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -997,80 +491,40 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="51">
+  <cellStyles count="5">
+    <cellStyle name="差" xfId="2" builtinId="27"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 2" xfId="49"/>
-    <cellStyle name="常规 3" xfId="50"/>
+    <cellStyle name="常规 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="常规 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="好" xfId="1" builtinId="26"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -1088,6 +542,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1374,26 +831,26 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N106"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9" style="13"/>
-    <col min="3" max="3" width="46.125" style="13" customWidth="1"/>
-    <col min="4" max="4" width="26.875" style="13" customWidth="1"/>
-    <col min="5" max="6" width="27.625" style="13" customWidth="1"/>
-    <col min="7" max="7" width="17.625" style="13" customWidth="1"/>
-    <col min="8" max="8" width="16.875" style="13" customWidth="1"/>
+    <col min="3" max="3" width="46.08984375" style="13" customWidth="1"/>
+    <col min="4" max="4" width="26.90625" style="13" customWidth="1"/>
+    <col min="5" max="6" width="27.6328125" style="13" customWidth="1"/>
+    <col min="7" max="7" width="17.6328125" style="13" customWidth="1"/>
+    <col min="8" max="8" width="16.90625" style="13" customWidth="1"/>
     <col min="9" max="10" width="16" style="13" customWidth="1"/>
-    <col min="11" max="14" width="9.625" style="13" customWidth="1"/>
+    <col min="11" max="14" width="9.6328125" style="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" spans="1:14">
+    <row r="1" spans="1:14" ht="14" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1412,22 +869,22 @@
       <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3" t="s">
+      <c r="H1" s="21"/>
+      <c r="I1" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3" t="s">
+      <c r="J1" s="21"/>
+      <c r="K1" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-    </row>
-    <row r="2" ht="13.5" spans="1:14">
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
+    </row>
+    <row r="2" spans="1:14" ht="14" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>9</v>
       </c>
@@ -1446,22 +903,22 @@
       <c r="F2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4" t="s">
+      <c r="H2" s="22"/>
+      <c r="I2" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4" t="s">
+      <c r="J2" s="22"/>
+      <c r="K2" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-    </row>
-    <row r="3" ht="13.5" spans="1:14">
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
+      <c r="N2" s="22"/>
+    </row>
+    <row r="3" spans="1:14" ht="14" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>9</v>
       </c>
@@ -1495,7 +952,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" ht="13.5" spans="1:14">
+    <row r="4" spans="1:14" ht="14" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>15</v>
       </c>
@@ -1513,7 +970,7 @@
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
     </row>
-    <row r="5" s="12" customFormat="1" spans="1:14">
+    <row r="5" spans="1:14" s="12" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
@@ -1557,12 +1014,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
       <c r="B6" s="17">
         <v>10011</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="D6" s="18"/>
       <c r="E6" s="18"/>
@@ -1571,7 +1028,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="18">
-        <v>4.35</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="I6" s="18">
         <v>0</v>
@@ -1586,7 +1043,7 @@
       <c r="M6" s="18"/>
       <c r="N6" s="18"/>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
       <c r="B7" s="1"/>
       <c r="D7" s="19"/>
       <c r="E7" s="19"/>
@@ -1600,7 +1057,7 @@
       <c r="M7" s="19"/>
       <c r="N7" s="19"/>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
       <c r="B8" s="1"/>
       <c r="C8" s="20"/>
       <c r="D8" s="19"/>
@@ -1615,7 +1072,7 @@
       <c r="M8" s="19"/>
       <c r="N8" s="19"/>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
       <c r="B9" s="1"/>
       <c r="C9" s="20"/>
       <c r="D9" s="19"/>
@@ -1630,7 +1087,7 @@
       <c r="M9" s="19"/>
       <c r="N9" s="19"/>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
       <c r="B10" s="1"/>
       <c r="C10" s="20"/>
       <c r="D10" s="19"/>
@@ -1645,7 +1102,7 @@
       <c r="M10" s="19"/>
       <c r="N10" s="19"/>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
       <c r="B11" s="1"/>
       <c r="C11" s="20"/>
       <c r="D11" s="19"/>
@@ -1660,7 +1117,7 @@
       <c r="M11" s="19"/>
       <c r="N11" s="19"/>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
       <c r="B12" s="1"/>
       <c r="C12" s="20"/>
       <c r="D12" s="19"/>
@@ -1675,7 +1132,7 @@
       <c r="M12" s="19"/>
       <c r="N12" s="19"/>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
       <c r="B13" s="1"/>
       <c r="C13" s="20"/>
       <c r="D13" s="19"/>
@@ -1690,7 +1147,7 @@
       <c r="M13" s="19"/>
       <c r="N13" s="19"/>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
       <c r="B14" s="1"/>
       <c r="C14" s="20"/>
       <c r="D14" s="19"/>
@@ -1705,7 +1162,7 @@
       <c r="M14" s="19"/>
       <c r="N14" s="19"/>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
       <c r="B15" s="1"/>
       <c r="C15" s="20"/>
       <c r="D15" s="19"/>
@@ -1720,7 +1177,7 @@
       <c r="M15" s="19"/>
       <c r="N15" s="19"/>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
       <c r="B16" s="1"/>
       <c r="C16" s="20"/>
       <c r="D16" s="19"/>
@@ -1735,7 +1192,7 @@
       <c r="M16" s="19"/>
       <c r="N16" s="19"/>
     </row>
-    <row r="17" spans="2:14">
+    <row r="17" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B17" s="1"/>
       <c r="C17" s="20"/>
       <c r="D17" s="19"/>
@@ -1750,7 +1207,7 @@
       <c r="M17" s="19"/>
       <c r="N17" s="19"/>
     </row>
-    <row r="18" spans="2:14">
+    <row r="18" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B18" s="1"/>
       <c r="C18" s="20"/>
       <c r="D18" s="19"/>
@@ -1765,7 +1222,7 @@
       <c r="M18" s="19"/>
       <c r="N18" s="19"/>
     </row>
-    <row r="19" spans="2:14">
+    <row r="19" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B19" s="1"/>
       <c r="C19" s="20"/>
       <c r="D19" s="19"/>
@@ -1780,7 +1237,7 @@
       <c r="M19" s="19"/>
       <c r="N19" s="19"/>
     </row>
-    <row r="20" spans="2:14">
+    <row r="20" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B20" s="1"/>
       <c r="C20" s="20"/>
       <c r="D20" s="19"/>
@@ -1795,7 +1252,7 @@
       <c r="M20" s="19"/>
       <c r="N20" s="19"/>
     </row>
-    <row r="21" spans="2:14">
+    <row r="21" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B21" s="1"/>
       <c r="C21" s="20"/>
       <c r="D21" s="19"/>
@@ -1810,7 +1267,7 @@
       <c r="M21" s="19"/>
       <c r="N21" s="19"/>
     </row>
-    <row r="22" spans="2:14">
+    <row r="22" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B22" s="1"/>
       <c r="C22" s="20"/>
       <c r="D22" s="19"/>
@@ -1825,7 +1282,7 @@
       <c r="M22" s="19"/>
       <c r="N22" s="19"/>
     </row>
-    <row r="23" spans="2:14">
+    <row r="23" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B23" s="1"/>
       <c r="C23" s="20"/>
       <c r="D23" s="19"/>
@@ -1840,7 +1297,7 @@
       <c r="M23" s="19"/>
       <c r="N23" s="19"/>
     </row>
-    <row r="24" spans="2:14">
+    <row r="24" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B24" s="1"/>
       <c r="C24" s="20"/>
       <c r="D24" s="19"/>
@@ -1855,7 +1312,7 @@
       <c r="M24" s="19"/>
       <c r="N24" s="19"/>
     </row>
-    <row r="25" spans="2:14">
+    <row r="25" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B25" s="1"/>
       <c r="C25" s="20"/>
       <c r="D25" s="19"/>
@@ -1870,7 +1327,7 @@
       <c r="M25" s="19"/>
       <c r="N25" s="19"/>
     </row>
-    <row r="26" spans="2:14">
+    <row r="26" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B26" s="1"/>
       <c r="C26" s="20"/>
       <c r="D26" s="19"/>
@@ -1885,7 +1342,7 @@
       <c r="M26" s="19"/>
       <c r="N26" s="19"/>
     </row>
-    <row r="27" spans="2:14">
+    <row r="27" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B27" s="1"/>
       <c r="C27" s="20"/>
       <c r="D27" s="19"/>
@@ -1900,7 +1357,7 @@
       <c r="M27" s="19"/>
       <c r="N27" s="19"/>
     </row>
-    <row r="28" spans="2:14">
+    <row r="28" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B28" s="1"/>
       <c r="C28" s="20"/>
       <c r="D28" s="19"/>
@@ -1915,7 +1372,7 @@
       <c r="M28" s="19"/>
       <c r="N28" s="19"/>
     </row>
-    <row r="29" spans="2:14">
+    <row r="29" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B29" s="1"/>
       <c r="C29" s="20"/>
       <c r="D29" s="19"/>
@@ -1930,7 +1387,7 @@
       <c r="M29" s="19"/>
       <c r="N29" s="19"/>
     </row>
-    <row r="30" spans="2:14">
+    <row r="30" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B30" s="1"/>
       <c r="C30" s="20"/>
       <c r="D30" s="19"/>
@@ -1945,7 +1402,7 @@
       <c r="M30" s="19"/>
       <c r="N30" s="19"/>
     </row>
-    <row r="31" spans="2:14">
+    <row r="31" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B31" s="1"/>
       <c r="C31" s="20"/>
       <c r="D31" s="19"/>
@@ -1960,7 +1417,7 @@
       <c r="M31" s="19"/>
       <c r="N31" s="19"/>
     </row>
-    <row r="32" spans="2:14">
+    <row r="32" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B32" s="1"/>
       <c r="C32" s="20"/>
       <c r="D32" s="19"/>
@@ -1975,7 +1432,7 @@
       <c r="M32" s="19"/>
       <c r="N32" s="19"/>
     </row>
-    <row r="33" spans="2:14">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B33" s="1"/>
       <c r="C33" s="20"/>
       <c r="D33" s="19"/>
@@ -1990,7 +1447,7 @@
       <c r="M33" s="19"/>
       <c r="N33" s="19"/>
     </row>
-    <row r="34" spans="2:14">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B34" s="1"/>
       <c r="C34" s="20"/>
       <c r="D34" s="19"/>
@@ -2005,7 +1462,7 @@
       <c r="M34" s="19"/>
       <c r="N34" s="19"/>
     </row>
-    <row r="35" spans="2:14">
+    <row r="35" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B35" s="1"/>
       <c r="C35" s="20"/>
       <c r="D35" s="19"/>
@@ -2020,7 +1477,7 @@
       <c r="M35" s="19"/>
       <c r="N35" s="19"/>
     </row>
-    <row r="36" spans="2:14">
+    <row r="36" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B36" s="1"/>
       <c r="C36" s="20"/>
       <c r="D36" s="19"/>
@@ -2035,7 +1492,7 @@
       <c r="M36" s="19"/>
       <c r="N36" s="19"/>
     </row>
-    <row r="37" spans="2:14">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B37" s="1"/>
       <c r="C37" s="20"/>
       <c r="D37" s="19"/>
@@ -2050,7 +1507,7 @@
       <c r="M37" s="19"/>
       <c r="N37" s="19"/>
     </row>
-    <row r="38" spans="2:14">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B38" s="1"/>
       <c r="C38" s="20"/>
       <c r="D38" s="19"/>
@@ -2065,7 +1522,7 @@
       <c r="M38" s="19"/>
       <c r="N38" s="19"/>
     </row>
-    <row r="39" spans="2:14">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B39" s="1"/>
       <c r="C39" s="20"/>
       <c r="D39" s="19"/>
@@ -2080,7 +1537,7 @@
       <c r="M39" s="19"/>
       <c r="N39" s="19"/>
     </row>
-    <row r="40" spans="2:14">
+    <row r="40" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B40" s="1"/>
       <c r="C40" s="20"/>
       <c r="D40" s="19"/>
@@ -2095,7 +1552,7 @@
       <c r="M40" s="19"/>
       <c r="N40" s="19"/>
     </row>
-    <row r="41" spans="2:14">
+    <row r="41" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B41" s="1"/>
       <c r="C41" s="20"/>
       <c r="D41" s="19"/>
@@ -2110,7 +1567,7 @@
       <c r="M41" s="19"/>
       <c r="N41" s="19"/>
     </row>
-    <row r="42" spans="2:14">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B42" s="1"/>
       <c r="C42" s="20"/>
       <c r="D42" s="19"/>
@@ -2125,7 +1582,7 @@
       <c r="M42" s="19"/>
       <c r="N42" s="19"/>
     </row>
-    <row r="43" spans="2:14">
+    <row r="43" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B43" s="1"/>
       <c r="C43" s="20"/>
       <c r="D43" s="19"/>
@@ -2140,7 +1597,7 @@
       <c r="M43" s="19"/>
       <c r="N43" s="19"/>
     </row>
-    <row r="44" spans="2:14">
+    <row r="44" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B44" s="1"/>
       <c r="C44" s="20"/>
       <c r="D44" s="19"/>
@@ -2155,7 +1612,7 @@
       <c r="M44" s="19"/>
       <c r="N44" s="19"/>
     </row>
-    <row r="45" spans="2:14">
+    <row r="45" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B45" s="1"/>
       <c r="C45" s="20"/>
       <c r="D45" s="19"/>
@@ -2170,7 +1627,7 @@
       <c r="M45" s="19"/>
       <c r="N45" s="19"/>
     </row>
-    <row r="46" spans="2:14">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B46" s="1"/>
       <c r="C46" s="20"/>
       <c r="D46" s="19"/>
@@ -2185,7 +1642,7 @@
       <c r="M46" s="19"/>
       <c r="N46" s="19"/>
     </row>
-    <row r="47" spans="2:14">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B47" s="1"/>
       <c r="C47" s="20"/>
       <c r="D47" s="19"/>
@@ -2200,7 +1657,7 @@
       <c r="M47" s="19"/>
       <c r="N47" s="19"/>
     </row>
-    <row r="48" spans="2:14">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B48" s="1"/>
       <c r="C48" s="20"/>
       <c r="D48" s="19"/>
@@ -2215,7 +1672,7 @@
       <c r="M48" s="19"/>
       <c r="N48" s="19"/>
     </row>
-    <row r="49" spans="2:14">
+    <row r="49" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B49" s="1"/>
       <c r="C49" s="20"/>
       <c r="D49" s="19"/>
@@ -2230,7 +1687,7 @@
       <c r="M49" s="19"/>
       <c r="N49" s="19"/>
     </row>
-    <row r="50" spans="2:14">
+    <row r="50" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B50" s="1"/>
       <c r="C50" s="20"/>
       <c r="D50" s="19"/>
@@ -2245,7 +1702,7 @@
       <c r="M50" s="19"/>
       <c r="N50" s="19"/>
     </row>
-    <row r="51" spans="2:14">
+    <row r="51" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B51" s="1"/>
       <c r="C51" s="20"/>
       <c r="D51" s="19"/>
@@ -2260,7 +1717,7 @@
       <c r="M51" s="19"/>
       <c r="N51" s="19"/>
     </row>
-    <row r="52" spans="2:14">
+    <row r="52" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B52" s="1"/>
       <c r="C52" s="20"/>
       <c r="D52" s="19"/>
@@ -2275,7 +1732,7 @@
       <c r="M52" s="19"/>
       <c r="N52" s="19"/>
     </row>
-    <row r="53" spans="2:14">
+    <row r="53" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B53" s="1"/>
       <c r="C53" s="20"/>
       <c r="D53" s="19"/>
@@ -2290,7 +1747,7 @@
       <c r="M53" s="19"/>
       <c r="N53" s="19"/>
     </row>
-    <row r="54" spans="2:14">
+    <row r="54" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B54" s="1"/>
       <c r="C54" s="20"/>
       <c r="D54" s="19"/>
@@ -2305,7 +1762,7 @@
       <c r="M54" s="19"/>
       <c r="N54" s="19"/>
     </row>
-    <row r="55" spans="2:14">
+    <row r="55" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B55" s="1"/>
       <c r="C55" s="20"/>
       <c r="D55" s="19"/>
@@ -2320,7 +1777,7 @@
       <c r="M55" s="19"/>
       <c r="N55" s="19"/>
     </row>
-    <row r="56" spans="2:14">
+    <row r="56" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B56" s="1"/>
       <c r="C56" s="20"/>
       <c r="D56" s="19"/>
@@ -2335,7 +1792,7 @@
       <c r="M56" s="19"/>
       <c r="N56" s="19"/>
     </row>
-    <row r="57" spans="2:14">
+    <row r="57" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B57" s="1"/>
       <c r="C57" s="20"/>
       <c r="D57" s="19"/>
@@ -2350,7 +1807,7 @@
       <c r="M57" s="19"/>
       <c r="N57" s="19"/>
     </row>
-    <row r="58" spans="2:14">
+    <row r="58" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B58" s="1"/>
       <c r="C58" s="20"/>
       <c r="D58" s="19"/>
@@ -2365,7 +1822,7 @@
       <c r="M58" s="19"/>
       <c r="N58" s="19"/>
     </row>
-    <row r="59" spans="2:14">
+    <row r="59" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B59" s="1"/>
       <c r="C59" s="20"/>
       <c r="D59" s="19"/>
@@ -2380,7 +1837,7 @@
       <c r="M59" s="19"/>
       <c r="N59" s="19"/>
     </row>
-    <row r="60" spans="2:14">
+    <row r="60" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B60" s="1"/>
       <c r="C60" s="20"/>
       <c r="D60" s="19"/>
@@ -2395,7 +1852,7 @@
       <c r="M60" s="19"/>
       <c r="N60" s="19"/>
     </row>
-    <row r="61" spans="2:14">
+    <row r="61" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B61" s="1"/>
       <c r="C61" s="20"/>
       <c r="D61" s="19"/>
@@ -2410,7 +1867,7 @@
       <c r="M61" s="19"/>
       <c r="N61" s="19"/>
     </row>
-    <row r="62" spans="2:14">
+    <row r="62" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B62" s="1"/>
       <c r="C62" s="20"/>
       <c r="D62" s="19"/>
@@ -2425,7 +1882,7 @@
       <c r="M62" s="19"/>
       <c r="N62" s="19"/>
     </row>
-    <row r="63" spans="2:14">
+    <row r="63" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B63" s="1"/>
       <c r="C63" s="20"/>
       <c r="D63" s="19"/>
@@ -2440,7 +1897,7 @@
       <c r="M63" s="19"/>
       <c r="N63" s="19"/>
     </row>
-    <row r="64" spans="2:14">
+    <row r="64" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B64" s="1"/>
       <c r="C64" s="20"/>
       <c r="D64" s="19"/>
@@ -2455,7 +1912,7 @@
       <c r="M64" s="19"/>
       <c r="N64" s="19"/>
     </row>
-    <row r="65" spans="2:14">
+    <row r="65" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B65" s="1"/>
       <c r="C65" s="20"/>
       <c r="D65" s="19"/>
@@ -2470,7 +1927,7 @@
       <c r="M65" s="19"/>
       <c r="N65" s="19"/>
     </row>
-    <row r="66" spans="2:14">
+    <row r="66" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B66" s="1"/>
       <c r="C66" s="20"/>
       <c r="D66" s="19"/>
@@ -2485,7 +1942,7 @@
       <c r="M66" s="19"/>
       <c r="N66" s="19"/>
     </row>
-    <row r="67" spans="2:14">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B67" s="1"/>
       <c r="C67" s="20"/>
       <c r="D67" s="19"/>
@@ -2500,7 +1957,7 @@
       <c r="M67" s="19"/>
       <c r="N67" s="19"/>
     </row>
-    <row r="68" spans="2:14">
+    <row r="68" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B68" s="1"/>
       <c r="C68" s="20"/>
       <c r="D68" s="19"/>
@@ -2515,7 +1972,7 @@
       <c r="M68" s="19"/>
       <c r="N68" s="19"/>
     </row>
-    <row r="69" spans="2:14">
+    <row r="69" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B69" s="1"/>
       <c r="C69" s="20"/>
       <c r="D69" s="19"/>
@@ -2530,7 +1987,7 @@
       <c r="M69" s="19"/>
       <c r="N69" s="19"/>
     </row>
-    <row r="70" spans="2:14">
+    <row r="70" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B70" s="1"/>
       <c r="C70" s="20"/>
       <c r="D70" s="19"/>
@@ -2545,7 +2002,7 @@
       <c r="M70" s="19"/>
       <c r="N70" s="19"/>
     </row>
-    <row r="71" spans="2:14">
+    <row r="71" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B71" s="1"/>
       <c r="C71" s="20"/>
       <c r="D71" s="19"/>
@@ -2560,7 +2017,7 @@
       <c r="M71" s="19"/>
       <c r="N71" s="19"/>
     </row>
-    <row r="72" spans="2:14">
+    <row r="72" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B72" s="1"/>
       <c r="C72" s="20"/>
       <c r="D72" s="19"/>
@@ -2575,7 +2032,7 @@
       <c r="M72" s="19"/>
       <c r="N72" s="19"/>
     </row>
-    <row r="73" spans="2:14">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B73" s="1"/>
       <c r="C73" s="20"/>
       <c r="D73" s="19"/>
@@ -2590,7 +2047,7 @@
       <c r="M73" s="19"/>
       <c r="N73" s="19"/>
     </row>
-    <row r="74" spans="2:14">
+    <row r="74" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B74" s="1"/>
       <c r="C74" s="20"/>
       <c r="D74" s="19"/>
@@ -2605,7 +2062,7 @@
       <c r="M74" s="19"/>
       <c r="N74" s="19"/>
     </row>
-    <row r="75" spans="2:14">
+    <row r="75" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B75" s="1"/>
       <c r="C75" s="20"/>
       <c r="D75" s="19"/>
@@ -2620,7 +2077,7 @@
       <c r="M75" s="19"/>
       <c r="N75" s="19"/>
     </row>
-    <row r="76" spans="2:14">
+    <row r="76" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B76" s="1"/>
       <c r="C76" s="20"/>
       <c r="D76" s="19"/>
@@ -2635,7 +2092,7 @@
       <c r="M76" s="19"/>
       <c r="N76" s="19"/>
     </row>
-    <row r="77" spans="2:14">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B77" s="1"/>
       <c r="C77" s="20"/>
       <c r="D77" s="19"/>
@@ -2650,7 +2107,7 @@
       <c r="M77" s="19"/>
       <c r="N77" s="19"/>
     </row>
-    <row r="78" spans="2:14">
+    <row r="78" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B78" s="1"/>
       <c r="C78" s="20"/>
       <c r="D78" s="19"/>
@@ -2665,7 +2122,7 @@
       <c r="M78" s="19"/>
       <c r="N78" s="19"/>
     </row>
-    <row r="79" spans="2:14">
+    <row r="79" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B79" s="1"/>
       <c r="C79" s="20"/>
       <c r="D79" s="19"/>
@@ -2680,7 +2137,7 @@
       <c r="M79" s="19"/>
       <c r="N79" s="19"/>
     </row>
-    <row r="80" spans="2:14">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B80" s="1"/>
       <c r="C80" s="20"/>
       <c r="D80" s="19"/>
@@ -2695,7 +2152,7 @@
       <c r="M80" s="19"/>
       <c r="N80" s="19"/>
     </row>
-    <row r="81" spans="2:14">
+    <row r="81" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B81" s="1"/>
       <c r="C81" s="20"/>
       <c r="D81" s="19"/>
@@ -2710,7 +2167,7 @@
       <c r="M81" s="19"/>
       <c r="N81" s="19"/>
     </row>
-    <row r="82" spans="2:14">
+    <row r="82" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B82" s="1"/>
       <c r="C82" s="20"/>
       <c r="D82" s="19"/>
@@ -2725,7 +2182,7 @@
       <c r="M82" s="19"/>
       <c r="N82" s="19"/>
     </row>
-    <row r="83" spans="2:14">
+    <row r="83" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B83" s="1"/>
       <c r="C83" s="20"/>
       <c r="D83" s="19"/>
@@ -2740,7 +2197,7 @@
       <c r="M83" s="19"/>
       <c r="N83" s="19"/>
     </row>
-    <row r="84" spans="2:14">
+    <row r="84" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B84" s="1"/>
       <c r="C84" s="20"/>
       <c r="D84" s="19"/>
@@ -2755,7 +2212,7 @@
       <c r="M84" s="19"/>
       <c r="N84" s="19"/>
     </row>
-    <row r="85" spans="2:14">
+    <row r="85" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B85" s="1"/>
       <c r="C85" s="20"/>
       <c r="D85" s="19"/>
@@ -2770,7 +2227,7 @@
       <c r="M85" s="19"/>
       <c r="N85" s="19"/>
     </row>
-    <row r="86" spans="2:14">
+    <row r="86" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B86" s="1"/>
       <c r="C86" s="20"/>
       <c r="D86" s="19"/>
@@ -2785,7 +2242,7 @@
       <c r="M86" s="19"/>
       <c r="N86" s="19"/>
     </row>
-    <row r="87" spans="2:14">
+    <row r="87" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B87" s="1"/>
       <c r="C87" s="20"/>
       <c r="D87" s="19"/>
@@ -2800,7 +2257,7 @@
       <c r="M87" s="19"/>
       <c r="N87" s="19"/>
     </row>
-    <row r="88" spans="2:14">
+    <row r="88" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B88" s="1"/>
       <c r="C88" s="20"/>
       <c r="D88" s="19"/>
@@ -2815,7 +2272,7 @@
       <c r="M88" s="19"/>
       <c r="N88" s="19"/>
     </row>
-    <row r="89" spans="2:14">
+    <row r="89" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B89" s="1"/>
       <c r="C89" s="20"/>
       <c r="D89" s="19"/>
@@ -2830,7 +2287,7 @@
       <c r="M89" s="19"/>
       <c r="N89" s="19"/>
     </row>
-    <row r="90" spans="2:14">
+    <row r="90" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B90" s="1"/>
       <c r="C90" s="20"/>
       <c r="D90" s="19"/>
@@ -2845,7 +2302,7 @@
       <c r="M90" s="19"/>
       <c r="N90" s="19"/>
     </row>
-    <row r="91" spans="2:14">
+    <row r="91" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B91" s="1"/>
       <c r="C91" s="20"/>
       <c r="D91" s="19"/>
@@ -2860,7 +2317,7 @@
       <c r="M91" s="19"/>
       <c r="N91" s="19"/>
     </row>
-    <row r="92" spans="2:14">
+    <row r="92" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B92" s="1"/>
       <c r="C92" s="20"/>
       <c r="D92" s="19"/>
@@ -2875,7 +2332,7 @@
       <c r="M92" s="19"/>
       <c r="N92" s="19"/>
     </row>
-    <row r="93" spans="2:14">
+    <row r="93" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B93" s="1"/>
       <c r="C93" s="20"/>
       <c r="D93" s="19"/>
@@ -2890,7 +2347,7 @@
       <c r="M93" s="19"/>
       <c r="N93" s="19"/>
     </row>
-    <row r="94" spans="2:14">
+    <row r="94" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B94" s="1"/>
       <c r="C94" s="20"/>
       <c r="D94" s="19"/>
@@ -2905,7 +2362,7 @@
       <c r="M94" s="19"/>
       <c r="N94" s="19"/>
     </row>
-    <row r="95" spans="2:14">
+    <row r="95" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B95" s="1"/>
       <c r="C95" s="20"/>
       <c r="D95" s="19"/>
@@ -2920,7 +2377,7 @@
       <c r="M95" s="19"/>
       <c r="N95" s="19"/>
     </row>
-    <row r="96" spans="2:14">
+    <row r="96" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B96" s="1"/>
       <c r="C96" s="20"/>
       <c r="D96" s="19"/>
@@ -2935,7 +2392,7 @@
       <c r="M96" s="19"/>
       <c r="N96" s="19"/>
     </row>
-    <row r="97" spans="2:14">
+    <row r="97" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B97" s="1"/>
       <c r="C97" s="20"/>
       <c r="D97" s="19"/>
@@ -2950,7 +2407,7 @@
       <c r="M97" s="19"/>
       <c r="N97" s="19"/>
     </row>
-    <row r="98" spans="2:14">
+    <row r="98" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B98" s="1"/>
       <c r="C98" s="20"/>
       <c r="D98" s="19"/>
@@ -2965,7 +2422,7 @@
       <c r="M98" s="19"/>
       <c r="N98" s="19"/>
     </row>
-    <row r="99" spans="2:14">
+    <row r="99" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B99" s="1"/>
       <c r="C99" s="20"/>
       <c r="D99" s="19"/>
@@ -2980,7 +2437,7 @@
       <c r="M99" s="19"/>
       <c r="N99" s="19"/>
     </row>
-    <row r="100" spans="2:14">
+    <row r="100" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B100" s="1"/>
       <c r="C100" s="20"/>
       <c r="D100" s="19"/>
@@ -2995,7 +2452,7 @@
       <c r="M100" s="19"/>
       <c r="N100" s="19"/>
     </row>
-    <row r="101" spans="2:14">
+    <row r="101" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B101" s="1"/>
       <c r="C101" s="20"/>
       <c r="D101" s="19"/>
@@ -3010,7 +2467,7 @@
       <c r="M101" s="19"/>
       <c r="N101" s="19"/>
     </row>
-    <row r="102" spans="2:14">
+    <row r="102" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B102" s="1"/>
       <c r="C102" s="20"/>
       <c r="D102" s="19"/>
@@ -3025,7 +2482,7 @@
       <c r="M102" s="19"/>
       <c r="N102" s="19"/>
     </row>
-    <row r="103" spans="2:14">
+    <row r="103" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B103" s="1"/>
       <c r="C103" s="20"/>
       <c r="D103" s="19"/>
@@ -3040,7 +2497,7 @@
       <c r="M103" s="19"/>
       <c r="N103" s="19"/>
     </row>
-    <row r="104" spans="2:14">
+    <row r="104" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B104" s="1"/>
       <c r="C104" s="20"/>
       <c r="D104" s="19"/>
@@ -3055,7 +2512,7 @@
       <c r="M104" s="19"/>
       <c r="N104" s="19"/>
     </row>
-    <row r="105" spans="2:14">
+    <row r="105" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B105" s="1"/>
       <c r="C105" s="20"/>
       <c r="D105" s="19"/>
@@ -3070,7 +2527,7 @@
       <c r="M105" s="19"/>
       <c r="N105" s="19"/>
     </row>
-    <row r="106" spans="2:14">
+    <row r="106" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B106" s="1"/>
       <c r="C106" s="20"/>
       <c r="D106" s="19"/>
@@ -3094,96 +2551,95 @@
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:N2"/>
   </mergeCells>
+  <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="B6">
     <cfRule type="duplicateValues" dxfId="0" priority="20"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AB14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="8.5" style="2" customWidth="1"/>
-    <col min="3" max="3" width="9.875" style="2" customWidth="1"/>
-    <col min="4" max="5" width="13.75" style="2" customWidth="1"/>
-    <col min="6" max="7" width="18.25" style="2" customWidth="1"/>
-    <col min="8" max="9" width="12.625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="8.5" style="2" customWidth="1"/>
+    <col min="2" max="2" width="8.453125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="9.90625" style="2" customWidth="1"/>
+    <col min="4" max="5" width="13.7265625" style="2" customWidth="1"/>
+    <col min="6" max="7" width="18.26953125" style="2" customWidth="1"/>
+    <col min="8" max="9" width="12.6328125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8.453125" style="2" customWidth="1"/>
     <col min="11" max="12" width="16" style="2" customWidth="1"/>
-    <col min="13" max="13" width="13.75" style="2" customWidth="1"/>
-    <col min="14" max="14" width="10.375" style="2" customWidth="1"/>
-    <col min="15" max="15" width="8.375" style="2" customWidth="1"/>
-    <col min="16" max="25" width="13.75" style="2" customWidth="1"/>
-    <col min="26" max="27" width="11.25" style="2" customWidth="1"/>
+    <col min="13" max="13" width="13.7265625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="10.36328125" style="2" customWidth="1"/>
+    <col min="15" max="15" width="8.36328125" style="2" customWidth="1"/>
+    <col min="16" max="25" width="13.7265625" style="2" customWidth="1"/>
+    <col min="26" max="27" width="11.26953125" style="2" customWidth="1"/>
     <col min="28" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="21"/>
+      <c r="F1" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="21"/>
+      <c r="H1" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="21"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="21"/>
+      <c r="M1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q1" s="21"/>
+      <c r="R1" s="21"/>
+      <c r="S1" s="21"/>
+      <c r="T1" s="21"/>
+      <c r="U1" s="21"/>
+      <c r="V1" s="21"/>
+      <c r="W1" s="21"/>
+      <c r="X1" s="21"/>
+      <c r="Y1" s="21"/>
+      <c r="Z1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="P1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-      <c r="U1" s="3"/>
-      <c r="V1" s="3"/>
-      <c r="W1" s="3"/>
-      <c r="X1" s="3"/>
-      <c r="Y1" s="3"/>
-      <c r="Z1" s="3" t="s">
+      <c r="AA1" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="AA1" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="AB1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:28">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>9</v>
       </c>
@@ -3193,25 +2649,25 @@
       <c r="C2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4" t="s">
+      <c r="E2" s="22"/>
+      <c r="F2" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4" t="s">
+      <c r="G2" s="22"/>
+      <c r="H2" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="4"/>
+      <c r="I2" s="22"/>
       <c r="J2" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="4"/>
+      <c r="L2" s="22"/>
       <c r="M2" s="4" t="s">
         <v>14</v>
       </c>
@@ -3221,18 +2677,18 @@
       <c r="O2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="P2" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="4"/>
+      <c r="P2" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q2" s="22"/>
+      <c r="R2" s="22"/>
+      <c r="S2" s="22"/>
+      <c r="T2" s="22"/>
+      <c r="U2" s="22"/>
+      <c r="V2" s="22"/>
+      <c r="W2" s="22"/>
+      <c r="X2" s="22"/>
+      <c r="Y2" s="22"/>
       <c r="Z2" s="4" t="s">
         <v>10</v>
       </c>
@@ -3240,7 +2696,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:28">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>9</v>
       </c>
@@ -3307,7 +2763,7 @@
       <c r="Z3" s="4"/>
       <c r="AA3" s="4"/>
     </row>
-    <row r="4" spans="1:28">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>15</v>
       </c>
@@ -3338,93 +2794,93 @@
       <c r="Z4" s="4"/>
       <c r="AA4" s="4"/>
     </row>
-    <row r="5" ht="36" customHeight="1" spans="1:28">
+    <row r="5" spans="1:28" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C5" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="E5" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="F5" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="G5" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="H5" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="I5" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="J5" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="K5" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="L5" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="M5" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="N5" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="O5" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="O5" s="6" t="s">
+      <c r="P5" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="P5" s="6" t="s">
+      <c r="Q5" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="Q5" s="6" t="s">
+      <c r="R5" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="R5" s="6" t="s">
+      <c r="S5" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="S5" s="6" t="s">
+      <c r="T5" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="T5" s="6" t="s">
+      <c r="U5" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="U5" s="6" t="s">
+      <c r="V5" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="V5" s="6" t="s">
+      <c r="W5" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="W5" s="6" t="s">
+      <c r="X5" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="X5" s="6" t="s">
+      <c r="Y5" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="Y5" s="6" t="s">
+      <c r="Z5" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="Z5" s="6" t="s">
+      <c r="AA5" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="AA5" s="6" t="s">
+      <c r="AB5" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="AB5" s="7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:28">
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B6" s="8">
         <v>1001100</v>
       </c>
@@ -3436,19 +2892,19 @@
         <v>2.8</v>
       </c>
       <c r="E6" s="8">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="F6" s="8">
         <v>2.8</v>
       </c>
       <c r="G6" s="8">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="H6" s="8">
         <v>2.8</v>
       </c>
       <c r="I6" s="8">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="J6" s="8">
         <v>1</v>
@@ -3457,7 +2913,7 @@
         <v>1.8</v>
       </c>
       <c r="L6" s="8">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="M6" s="8">
         <v>90</v>
@@ -3472,7 +2928,7 @@
         <v>-2.65</v>
       </c>
       <c r="Q6" s="8">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="R6" s="8">
         <v>-2.65</v>
@@ -3496,38 +2952,38 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:28">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B7" s="8">
         <v>1001101</v>
       </c>
       <c r="C7" s="8" t="str">
-        <f t="shared" ref="C7:C70" si="0">LEFT(B7,6)</f>
+        <f t="shared" ref="C7:C14" si="0">LEFT(B7,6)</f>
         <v>100110</v>
       </c>
       <c r="D7" s="8">
         <v>2.8</v>
       </c>
       <c r="E7" s="8">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="F7" s="8">
         <v>2.8</v>
       </c>
       <c r="G7" s="8">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="H7" s="8">
         <v>2.8</v>
       </c>
       <c r="I7" s="8">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="J7" s="8"/>
       <c r="K7" s="8">
         <v>1.8</v>
       </c>
       <c r="L7" s="8">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="M7" s="8">
         <v>90</v>
@@ -3542,7 +2998,7 @@
         <v>-2.65</v>
       </c>
       <c r="Q7" s="8">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="R7" s="8">
         <v>-2.65</v>
@@ -3566,7 +3022,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:28">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B8" s="8">
         <v>1001102</v>
       </c>
@@ -3578,26 +3034,26 @@
         <v>2.8</v>
       </c>
       <c r="E8" s="8">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="F8" s="8">
         <v>2.8</v>
       </c>
       <c r="G8" s="8">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="H8" s="8">
         <v>2.8</v>
       </c>
       <c r="I8" s="8">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="J8" s="8"/>
       <c r="K8" s="8">
         <v>1.8</v>
       </c>
       <c r="L8" s="8">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="M8" s="8">
         <v>90</v>
@@ -3612,7 +3068,7 @@
         <v>-2.65</v>
       </c>
       <c r="Q8" s="8">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="R8" s="8">
         <v>-2.65</v>
@@ -3636,7 +3092,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:28">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B9" s="10">
         <v>1001200</v>
       </c>
@@ -3648,19 +3104,19 @@
         <v>2.8</v>
       </c>
       <c r="E9" s="10">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="F9" s="10">
         <v>2.8</v>
       </c>
       <c r="G9" s="10">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="H9" s="10">
         <v>2.8</v>
       </c>
       <c r="I9" s="10">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="J9" s="10">
         <v>1</v>
@@ -3669,7 +3125,7 @@
         <v>1.8</v>
       </c>
       <c r="L9" s="10">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="M9" s="10">
         <v>90</v>
@@ -3684,7 +3140,7 @@
         <v>-2.65</v>
       </c>
       <c r="Q9" s="10">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="R9" s="10">
         <v>-2.65</v>
@@ -3708,7 +3164,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:28">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B10" s="10">
         <v>1001201</v>
       </c>
@@ -3720,26 +3176,26 @@
         <v>2.8</v>
       </c>
       <c r="E10" s="10">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="F10" s="10">
         <v>2.8</v>
       </c>
       <c r="G10" s="10">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="H10" s="10">
         <v>2.8</v>
       </c>
       <c r="I10" s="10">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="J10" s="10"/>
       <c r="K10" s="10">
         <v>1.8</v>
       </c>
       <c r="L10" s="10">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="M10" s="10">
         <v>90</v>
@@ -3754,7 +3210,7 @@
         <v>-2.65</v>
       </c>
       <c r="Q10" s="10">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="R10" s="10">
         <v>-2.65</v>
@@ -3778,7 +3234,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:28">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B11" s="10">
         <v>1001202</v>
       </c>
@@ -3790,26 +3246,26 @@
         <v>2.8</v>
       </c>
       <c r="E11" s="10">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="F11" s="10">
         <v>2.8</v>
       </c>
       <c r="G11" s="10">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="H11" s="10">
         <v>2.8</v>
       </c>
       <c r="I11" s="10">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="J11" s="10"/>
       <c r="K11" s="10">
         <v>1.8</v>
       </c>
       <c r="L11" s="10">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="M11" s="10">
         <v>90</v>
@@ -3824,7 +3280,7 @@
         <v>-2.65</v>
       </c>
       <c r="Q11" s="10">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="R11" s="10">
         <v>-2.65</v>
@@ -3848,7 +3304,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:28">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B12" s="10">
         <v>1001210</v>
       </c>
@@ -3860,19 +3316,19 @@
         <v>-2.65</v>
       </c>
       <c r="E12" s="10">
-        <v>5.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="F12" s="10">
         <v>-2.65</v>
       </c>
       <c r="G12" s="10">
-        <v>5.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="H12" s="10">
         <v>-2.65</v>
       </c>
       <c r="I12" s="10">
-        <v>5.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="J12" s="10">
         <v>1</v>
@@ -3881,7 +3337,7 @@
         <v>-2.65</v>
       </c>
       <c r="L12" s="10">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="M12" s="10">
         <v>180</v>
@@ -3916,7 +3372,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:28">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B13" s="10">
         <v>1001211</v>
       </c>
@@ -3928,26 +3384,26 @@
         <v>-2.65</v>
       </c>
       <c r="E13" s="10">
-        <v>5.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="F13" s="10">
         <v>-2.65</v>
       </c>
       <c r="G13" s="10">
-        <v>5.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="H13" s="10">
         <v>-2.65</v>
       </c>
       <c r="I13" s="10">
-        <v>5.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="J13" s="10"/>
       <c r="K13" s="10">
         <v>-2.65</v>
       </c>
       <c r="L13" s="10">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="M13" s="10">
         <v>180</v>
@@ -3982,7 +3438,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:28">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B14" s="10">
         <v>1001212</v>
       </c>
@@ -3994,26 +3450,26 @@
         <v>-2.65</v>
       </c>
       <c r="E14" s="10">
-        <v>5.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="F14" s="10">
         <v>-2.65</v>
       </c>
       <c r="G14" s="10">
-        <v>5.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="H14" s="10">
         <v>-2.65</v>
       </c>
       <c r="I14" s="10">
-        <v>5.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="J14" s="10"/>
       <c r="K14" s="10">
         <v>-2.65</v>
       </c>
       <c r="L14" s="10">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="M14" s="10">
         <v>180</v>
@@ -4050,19 +3506,19 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="P2:Y2"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="P1:Y1"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="P2:Y2"/>
   </mergeCells>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>